--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -19829,7 +19829,10 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Attack Power = Weapon Damage x (1 + STR / 200)
-Effective Equipment WT = Equipment WT x (1 - STR / (200 + STR))
+Effective Equipment WT:
+  If Equipment WT &gt;= 0: Effective WT = Equipment WT x (1 - STR / (200 + STR))  [STR reduces burden]
+  If Equipment WT &lt; 0: Effective WT = Equipment WT x (1 + STR / (200 + STR))  [STR amplifies speed bonus]
+  Cap: pending — to be determined during balancing.
 RT Delay Bonus = Base RT Delay x (1 + min(STR / (200 + STR), 0.75))
 Force = 1 + floor(STR / 60)</t>
         </is>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -1837,12 +1837,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Natural in-battle MP regeneration</t>
+          <t>Natural MP Regen and Persistent HP/MP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INT does not provide natural in-battle MP regeneration. Units normally begin battle at full MP. MP is restored only by explicitly authored Skills, statuses, passives, items, map objects, battle conditions, Doctrines, Augments, or other effects.</t>
+          <t>INT provides natural in-battle MP regeneration as a visible Derived Stat. MP Regen = 2 + floor(INT / 40) MP per 1000 CT. Base 2 ensures all units regenerate naturally. Every 40 INT adds +1. No cap. HP and MP persist between battles — battles start at persistent current values, NOT full. Post-battle recovery: ceil(Max × 0.35) for all surviving units. Skill MP Cost scales with Weapon Level: Effective MP Cost = ceil(Base MP Cost × Scale(Weapon Level)). Full rules: query persistent_hp_mp_rules and core_stats in CTRBLXAI.db.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -19768,7 +19768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INT (Skill Potency, Max MP, Bonus Skill Range, and other explicitly authored INT interactions)</t>
+          <t>INT (Skill Potency, Max MP, Bonus Skill Range, MP Regen, and other explicitly authored INT interactions)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -19882,12 +19882,13 @@
           <t>Skill Potency Multiplier = 1 + INT / (200 + INT)
 Skill Potency Bonus = Skill Potency Multiplier - 1
 Max MP = 20 + INT x 2
-Bonus Skill Range = floor(INT / 75) + Flat Skill Range Bonuses</t>
+Bonus Skill Range = floor(INT / 75) + Flat Skill Range Bonuses
+MP Regen = 2 + floor(INT / 40) MP per 1000 CT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INT does not provide natural in-battle MP regeneration or automatic ready-turn MP recovery. Units normally begin battle at full MP unless an authored encounter, scenario, status, map condition, or other rule says otherwise. Explicit MP recovery remains valid through authored Skills, statuses, passives, items, map objects, battle conditions, Doctrines, Augments, and other effects. Skill Potency applies only where explicitly declared. Bonus Skill Range changes targeting distance only and does not enlarge Pattern or AOE dimensions unless explicitly stated.</t>
+          <t>MP Regen: base 2 + floor(INT/40). No cap. CT-based accumulator. Arcane Flow (ready-turn passive) is separate. Skill MP Cost: each skill has authored formula round(Base + Growth × (L-1)).</t>
         </is>
       </c>
     </row>
@@ -20845,6 +20846,58 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Persistent HP/MP</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Persistent Resources</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Battle Start HP = Persistent Current HP. Battle Start MP = Persistent Current MP.
+Post-Battle Recovery = ceil(Max HP × 0.35) + ceil(Max MP × 0.35) for ALL surviving owned units (deployed or benched).
+KO units: zero recovery, cleared only at base.
+Base: replenishes Item charges but does NOT restore HP or MP.
+Max increase: Current += New Max − Old Max. Max decrease: Current = min(Current, New Max).</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Locked. Full rules in persistent_hp_mp_rules table (CTRBLXAI.db).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Persistent HP/MP</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MP Regen</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MP Regen = 2 + floor(INT / 40) MP per 1000 CT.
+Base 2 ensures all units regenerate. Every 40 INT adds +1. No cap.
+Accumulator += CT Passed × MP Regen / 1000. When ≥ 1: restore floor(Accumulator) MP.
+Reference: INT 0=2, INT 40=3, INT 80=4, INT 120=5, INT 160=6, INT 200=7.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Locked. Visible Derived Stat. Linear and predictable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
   </sheetData>
   <autoFilter ref="A1:D49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -39290,7 +39343,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scales through Effective Skill Level, not actual Max MP. Example: MP Cost = Base MP Cost + MP Growth x (Effective Skill Level - 1). Round once at final result. May be zero. No separate burden field exists.</t>
+          <t>MP Cost uses authored per-skill formula: round(Base + Growth × (Effective Skill Level - 1)). Effective Skill Level = Main-hand Item Level = Weapon Level. Each skill has its own base cost and growth rate. May be zero.</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -19768,7 +19768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20897,7 +20897,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
   </sheetData>
   <autoFilter ref="A1:D49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37836,7 +37835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -39226,6 +39225,38 @@
       <c r="F46" t="inlineStr">
         <is>
           <t>All main stats -10%. Does not stack with itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Statuses Buff</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Buff (Dispellable)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1 turn (until next ready turn)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Refresh duration</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Reduces incoming final damage by 35% (base). Guard Bonus passives add to mitigation (e.g., Shield +15%). Total capped at 80%. Dispellable by Purge/Dispel. Removed by hard CC (Stun, Freeze, Sleep). Guard RT = round(Modified Base RT × 0.10) + 50% Effective Armor Off-Hand WT. 2H weapon → Off-Hand WT = 0. Once per turn, 1 AP.</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2293,6 +2293,353 @@
       <c r="D80" t="inlineStr">
         <is>
           <t>All Slice 1 checklist items verified complete via code audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ACTION MENU PRESENTATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Top-level menu</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>COMMANDS | SKILLS | ITEMS | WAIT. STANCE removed.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Commands submenu</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MOVE | BASIC ATTACK | GUARD | PUSH | INTERACT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>After execution</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Return to top-level if unit may continue. Do not return to submenu. If turn ends, wait for authoritative turn state.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Top-level. If AP remains, opens confirmation before ending turn.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Button availability</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Never remove/hide unavailable buttons. Gray out + tooltip explaining why.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Availability source</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Reasons come from owning functional system. Slice 7 displays but does not create gameplay rules.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Push</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Visible but unavailable until Slice 2 displacement + Slice 3 command pipeline implemented.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Interact</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Visible but unavailable until object-interaction dependencies exist.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Back/Confirm</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Fixed positions: Back bottom-left, Confirm bottom-right. Stable across all menus. Confirm unavailable until selection valid.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Back navigation</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Command targeting→Commands. Skill targeting→Skills. Item targeting→Items. Submenu→top-level.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PUSH ACTION (Universal Command)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Push AP Cost</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1 AP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Push RT Cost</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>round(Modified Base RT x 0.10). Gloves WT already in Modified Base RT.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Push Range</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1 (adjacent only). Gloves passives may extend.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Push Direction</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Directly away from pusher. GL-013 overrides for adjacent.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Push Distance</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>max(0, Force - Target Stability) tiles.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Force</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1 + floor(STR / 60)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1 + floor(VIT / 60)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EQUIPMENT WT MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Non-weapon WT</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Body, Head, Gloves, Feet, Accessory WT adds to Base RT always.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Weapon WT</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Only applies during Basic Attack or Skills via Effective WT formula.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Locked</t>
         </is>
       </c>
     </row>
@@ -2505,6 +2852,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -4328,6 +4676,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -6010,6 +6359,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -6027,6 +6377,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -6238,6 +6589,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
@@ -6371,6 +6723,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
@@ -6666,6 +7019,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
@@ -6871,6 +7225,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
@@ -10097,6 +10452,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -10356,6 +10712,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -10927,6 +11284,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -11713,6 +12071,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -19910,7 +20269,7 @@
 Defense Power = Defense x (1 + VIT / 300)
 Debuff Resistance Multiplier = 1 - VIT / (300 + VIT)
 RT Delay Resistance = Incoming RT Delay x (1 - VIT / (300 + VIT))
-Stability = 1 + floor(VIT / 60)</t>
+Stability = floor(VIT / 60)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20846,6 +21205,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -27081,7 +27441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:AC18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28728,6 +29088,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -29320,6 +29681,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -30328,6 +30690,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -31268,6 +31631,8 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -31808,6 +32173,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -34017,6 +34383,8 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -34579,6 +34947,8 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
@@ -35146,6 +35516,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -35820,6 +36191,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
@@ -39617,6 +39989,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
@@ -39629,6 +40002,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -42,7 +42,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03 Movement Targeting'!$A$1:$D$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04 Elements Statuses'!$A$1:$D$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05b Skill Catalog'!$A$1:$V$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'06b Augment Catalog'!$A$1:$X$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'06b Augment Catalog'!$A$1:$X$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'07 Doctrines'!$A$1:$AG$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'10 Loot Progression'!$A$1:$D$82</definedName>
   </definedNames>
@@ -2296,7 +2296,6 @@
         </is>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -2474,7 +2473,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -2601,7 +2599,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
@@ -2852,7 +2849,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -4676,7 +4672,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -6359,7 +6354,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -6377,7 +6371,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -6589,7 +6582,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
@@ -6723,7 +6715,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7010,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7215,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
@@ -10452,7 +10441,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -10712,7 +10700,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -11284,7 +11271,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -12071,7 +12057,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -21205,7 +21190,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -27441,7 +27425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="C1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29088,7 +29072,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -29681,7 +29664,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -30690,7 +30672,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -31631,8 +31612,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -32173,7 +32152,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -34383,8 +34361,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -34947,8 +34923,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
@@ -35516,7 +35490,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -36191,7 +36164,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
@@ -39989,7 +39961,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
@@ -40002,7 +39973,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
@@ -51733,7 +51703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X112"/>
+  <dimension ref="A1:X113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -62745,852 +62715,852 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
+          <t>AUG-SHARED-RESOLVE</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Shared Resolve</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Targeting</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Self (exact — not 'Ally Unit, Self' or 'Self, Allies')</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Skill must not apply Hide, Counter Stance, Riposte, Reaction, untargetability, or any effect that grants counter-attack or reaction abilities. Skill must not already be an aura or AOE buff. Skill must apply standard stat/combat buffs only (Frenzy, Haste, Rush, Regeneration, Recharge, Blessed, Enlightened, Overflow, or numerical stat modifiers).</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Change the supported Skill's target from Self to All Standing Allies (including caster), regardless of range. The Skill's buff effects are applied to each valid ally individually using the caster's stats at resolution.</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>MP + RT</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>MP Cost ×3.00; RT Cost ×2.00</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>At Skill commitment (targeting override applied before resolution)</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Once per supported resolution</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>Caster stats snapshot at commitment; buff applied to each ally at resolution using caster's snapshot</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>Original caster owns all applied buffs</t>
+        </is>
+      </c>
+      <c r="O91" s="5" t="inlineStr">
+        <is>
+          <t>N/A (buff application only)</t>
+        </is>
+      </c>
+      <c r="P91" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q91" s="5" t="inlineStr">
+        <is>
+          <t>Cannot be attached to a Skill that already targets allies or has an AOE pattern. Cannot stack with any other targeting-conversion augment on the same Skill.</t>
+        </is>
+      </c>
+      <c r="R91" s="5" t="inlineStr">
+        <is>
+          <t>Buffs applied to allies do not inherit or retrigger this Augment. Buff Delivery augments on the same Skill do NOT apply per-ally (they fire once for the caster's resolution, not per recipient).</t>
+        </is>
+      </c>
+      <c r="S91" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T91" s="5" t="inlineStr">
+        <is>
+          <t>Acquisition scarcity only; exact band pending</t>
+        </is>
+      </c>
+      <c r="U91" s="5" t="inlineStr">
+        <is>
+          <t>Working simulation baseline; not final balance</t>
+        </is>
+      </c>
+      <c r="V91" s="5" t="inlineStr">
+        <is>
+          <t>Complete working profile</t>
+        </is>
+      </c>
+      <c r="W91" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="X91" s="5" t="inlineStr">
+        <is>
+          <t>First targeting-conversion augment. Converts self-buff into party-wide buff at ×3 MP and ×2 RT. No range limit — full map broadcast. Strict eligibility: only standard stat/combat buffs (no Hide, Counter, Reaction, untargetability, auras). Current eligible skills: Battle Fury, Mana Surge. Future Self-only Buff skills auto-qualify if they meet requirements. The ×3 MP cost means this is typically a once-per-battle ability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
           <t>AUG-BURNING-GROUND</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Burning Ground</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>Terrain Effect</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Fire</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H92" s="6" t="inlineStr">
         <is>
           <t>Tiles affected by the supported Skill gain Burning for 900 CT.</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="J92" s="6" t="inlineStr">
         <is>
           <t>MP Cost ×1.20</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="K92" s="6" t="inlineStr">
         <is>
           <t>As effect states</t>
         </is>
       </c>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="L92" s="6" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M92" s="6" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="N92" s="6" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O91" s="5" t="inlineStr">
+      <c r="O92" s="6" t="inlineStr">
         <is>
           <t>As compatible Skill defines</t>
         </is>
       </c>
-      <c r="P91" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q91" s="5" t="inlineStr">
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
         <is>
           <t>Use normal terrain compatibility, ownership, duration, and element reactions.</t>
         </is>
       </c>
-      <c r="R91" s="5" t="inlineStr">
+      <c r="R92" s="6" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S91" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T91" s="5" t="inlineStr">
+      <c r="S92" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T92" s="6" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U91" s="5" t="inlineStr">
+      <c r="U92" s="6" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V91" s="5" t="inlineStr">
+      <c r="V92" s="6" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W91" s="5" t="inlineStr">
+      <c r="W92" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X91" s="5" t="inlineStr">
+      <c r="X92" s="6" t="inlineStr">
         <is>
           <t>Migrated from v0.8 baseline with v0.9 safety clarifications</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>AUG-DARKENED-GROUND</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Darkened Ground</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Terrain Effect</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>After the supported Skill resolves, create Darkened Ground on the target's tile and adjacent tiles (cross pattern, 5 tiles). Units on Darkened Ground have -20% healing received. Lasts 3 turns.</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J92" s="5" t="inlineStr">
+      <c r="J93" s="6" t="inlineStr">
         <is>
           <t>MP Cost ×1.20</t>
         </is>
       </c>
-      <c r="K92" s="5" t="inlineStr">
+      <c r="K93" s="6" t="inlineStr">
         <is>
           <t>After Skill resolution completes</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="L93" s="6" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M92" s="5" t="inlineStr">
+      <c r="M93" s="6" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N92" s="5" t="inlineStr">
+      <c r="N93" s="6" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O92" s="5" t="inlineStr">
+      <c r="O93" s="6" t="inlineStr">
         <is>
           <t>N/A (debuff zone, not damage)</t>
         </is>
       </c>
-      <c r="P92" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q92" s="5" t="inlineStr">
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
         <is>
           <t>Terrain overwrites existing terrain effects on the same tiles.</t>
         </is>
       </c>
-      <c r="R92" s="5" t="inlineStr">
+      <c r="R93" s="6" t="inlineStr">
         <is>
           <t>Terrain effects do not inherit/retrigger any Augment.</t>
         </is>
       </c>
-      <c r="S92" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T92" s="5" t="inlineStr">
+      <c r="S93" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T93" s="6" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U92" s="5" t="inlineStr">
+      <c r="U93" s="6" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V92" s="5" t="inlineStr">
+      <c r="V93" s="6" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W92" s="5" t="inlineStr">
+      <c r="W93" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X92" s="5" t="inlineStr">
+      <c r="X93" s="6" t="inlineStr">
         <is>
           <t>Anti-healing terrain. Doesn't deal damage directly but reduces enemy sustain. Zoning tool against healing-heavy compositions.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>AUG-ELECTRIC-FIELD</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Electric Field</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>Terrain Effect</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>After the supported Skill resolves, create Electric Field terrain on the target's tile and adjacent tiles (cross pattern, 5 tiles). Electric Field deals Electric damage to any unit ending their turn on it. Lasts 2 turns.</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I94" s="6" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="J94" s="6" t="inlineStr">
         <is>
           <t>MP Cost ×1.25</t>
         </is>
       </c>
-      <c r="K93" s="5" t="inlineStr">
+      <c r="K94" s="6" t="inlineStr">
         <is>
           <t>After Skill resolution completes</t>
         </is>
       </c>
-      <c r="L93" s="5" t="inlineStr">
+      <c r="L94" s="6" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M93" s="5" t="inlineStr">
+      <c r="M94" s="6" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N93" s="5" t="inlineStr">
+      <c r="N94" s="6" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O93" s="5" t="inlineStr">
+      <c r="O94" s="6" t="inlineStr">
         <is>
           <t>Electric (terrain damage)</t>
         </is>
       </c>
-      <c r="P93" s="5" t="inlineStr">
+      <c r="P94" s="6" t="inlineStr">
         <is>
           <t>Terrain damage credits original caster</t>
         </is>
       </c>
-      <c r="Q93" s="5" t="inlineStr">
+      <c r="Q94" s="6" t="inlineStr">
         <is>
           <t>Terrain overwrites existing terrain effects on the same tiles.</t>
         </is>
       </c>
-      <c r="R93" s="5" t="inlineStr">
+      <c r="R94" s="6" t="inlineStr">
         <is>
           <t>Terrain damage does not inherit/retrigger any Augment.</t>
         </is>
       </c>
-      <c r="S93" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T93" s="5" t="inlineStr">
+      <c r="S94" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T94" s="6" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U93" s="5" t="inlineStr">
+      <c r="U94" s="6" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V93" s="5" t="inlineStr">
+      <c r="V94" s="6" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W93" s="5" t="inlineStr">
+      <c r="W94" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X93" s="5" t="inlineStr">
+      <c r="X94" s="6" t="inlineStr">
         <is>
           <t>Electric terrain variant. Area denial. Synergizes with Wet status — Wet units on Electric Field take bonus damage per element interaction rules.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>AUG-FROZEN-GROUND</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Frozen Ground</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Terrain Effect</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>Ice;  or Ground</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>Tiles affected by the supported Skill gain Frozen for 900 CT.</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I95" s="6" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J94" s="5" t="inlineStr">
+      <c r="J95" s="6" t="inlineStr">
         <is>
           <t>MP Cost ×1.20</t>
         </is>
       </c>
-      <c r="K94" s="5" t="inlineStr">
+      <c r="K95" s="6" t="inlineStr">
         <is>
           <t>As effect states</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="L95" s="6" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M94" s="5" t="inlineStr">
+      <c r="M95" s="6" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N94" s="5" t="inlineStr">
+      <c r="N95" s="6" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O94" s="5" t="inlineStr">
+      <c r="O95" s="6" t="inlineStr">
         <is>
           <t>As compatible Skill defines</t>
         </is>
       </c>
-      <c r="P94" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q94" s="5" t="inlineStr">
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q95" s="6" t="inlineStr">
         <is>
           <t>Use normal terrain compatibility, ownership, duration, and element reactions.</t>
         </is>
       </c>
-      <c r="R94" s="5" t="inlineStr">
+      <c r="R95" s="6" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S94" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T94" s="5" t="inlineStr">
+      <c r="S95" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T95" s="6" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U94" s="5" t="inlineStr">
+      <c r="U95" s="6" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V94" s="5" t="inlineStr">
+      <c r="V95" s="6" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W94" s="5" t="inlineStr">
+      <c r="W95" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X94" s="5" t="inlineStr">
+      <c r="X95" s="6" t="inlineStr">
         <is>
           <t>Migrated from v0.8 baseline with v0.9 safety clarifications</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>AUG-HOLY-GROUND</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Holy Ground</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>Terrain Effect</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D96" s="6" t="inlineStr">
         <is>
           <t>Direct Damage OR Support OR Healing</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>After the supported Skill resolves, create Holy Ground on the caster's tile and adjacent tiles (cross pattern, 5 tiles). Ally units on Holy Ground recover 5% max HP at turn start. Damages Undead units for 5% max HP. Lasts 2 turns.</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J95" s="5" t="inlineStr">
+      <c r="J96" s="6" t="inlineStr">
         <is>
           <t>MP Cost ×1.30</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="K96" s="6" t="inlineStr">
         <is>
           <t>After Skill resolution completes</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="L96" s="6" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M95" s="5" t="inlineStr">
+      <c r="M96" s="6" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N95" s="5" t="inlineStr">
+      <c r="N96" s="6" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O95" s="5" t="inlineStr">
+      <c r="O96" s="6" t="inlineStr">
         <is>
           <t>Holy (terrain healing/damage)</t>
         </is>
       </c>
-      <c r="P95" s="5" t="inlineStr">
+      <c r="P96" s="6" t="inlineStr">
         <is>
           <t>Terrain damage credits original caster</t>
         </is>
       </c>
-      <c r="Q95" s="5" t="inlineStr">
+      <c r="Q96" s="6" t="inlineStr">
         <is>
           <t>Terrain overwrites existing terrain effects on the same tiles.</t>
         </is>
       </c>
-      <c r="R95" s="5" t="inlineStr">
+      <c r="R96" s="6" t="inlineStr">
         <is>
           <t>Terrain effects do not inherit/retrigger any Augment.</t>
         </is>
       </c>
-      <c r="S95" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T95" s="5" t="inlineStr">
+      <c r="S96" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T96" s="6" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U95" s="5" t="inlineStr">
+      <c r="U96" s="6" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V95" s="5" t="inlineStr">
+      <c r="V96" s="6" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W95" s="5" t="inlineStr">
+      <c r="W96" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X95" s="5" t="inlineStr">
+      <c r="X96" s="6" t="inlineStr">
         <is>
           <t>Ally-beneficial terrain. Placed on caster's position (defensive). Hold-ground incentive — stay in the zone for healing. Anti-Undead utility per Holy element rules.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>AUG-POISON-CLOUD</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Poison Cloud</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Terrain Effect</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Poison;  or Ground</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>Tiles affected by the supported Skill gain Poison Cloud for 1500 CT.</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J96" s="5" t="inlineStr">
+      <c r="J97" s="6" t="inlineStr">
         <is>
           <t>MP Cost ×1.20</t>
         </is>
       </c>
-      <c r="K96" s="5" t="inlineStr">
+      <c r="K97" s="6" t="inlineStr">
         <is>
           <t>As effect states</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L97" s="6" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M96" s="5" t="inlineStr">
+      <c r="M97" s="6" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N96" s="5" t="inlineStr">
+      <c r="N97" s="6" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O96" s="5" t="inlineStr">
+      <c r="O97" s="6" t="inlineStr">
         <is>
           <t>As compatible Skill defines</t>
         </is>
       </c>
-      <c r="P96" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q96" s="5" t="inlineStr">
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
         <is>
           <t>Use normal terrain compatibility, ownership, duration, and element reactions.</t>
         </is>
       </c>
-      <c r="R96" s="5" t="inlineStr">
+      <c r="R97" s="6" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S96" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T96" s="5" t="inlineStr">
+      <c r="S97" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T97" s="6" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U96" s="5" t="inlineStr">
+      <c r="U97" s="6" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V96" s="5" t="inlineStr">
+      <c r="V97" s="6" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W96" s="5" t="inlineStr">
+      <c r="W97" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X96" s="5" t="inlineStr">
-        <is>
-          <t>Migrated from v0.8 baseline with v0.9 safety clarifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>AUG-WET-GROUND</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Wet Ground</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Terrain Effect</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Enemy Unit</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>Water;  or Ground</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>Tiles affected by the supported Skill gain Wet for 1500 CT.</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>MP Cost ×1.15</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>As effect states</t>
-        </is>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>Once per supported resolution</t>
-        </is>
-      </c>
-      <c r="M97" s="5" t="inlineStr">
-        <is>
-          <t>At Skill commitment; remains through resolution</t>
-        </is>
-      </c>
-      <c r="N97" s="5" t="inlineStr">
-        <is>
-          <t>Original caster</t>
-        </is>
-      </c>
-      <c r="O97" s="5" t="inlineStr">
-        <is>
-          <t>As compatible Skill defines</t>
-        </is>
-      </c>
-      <c r="P97" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q97" s="5" t="inlineStr">
-        <is>
-          <t>Use normal terrain compatibility, ownership, duration, and element reactions.</t>
-        </is>
-      </c>
-      <c r="R97" s="5" t="inlineStr">
-        <is>
-          <t>Secondary effects do not inherit/retrigger this Augment.</t>
-        </is>
-      </c>
-      <c r="S97" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T97" s="5" t="inlineStr">
-        <is>
-          <t>Acquisition scarcity only; exact band pending</t>
-        </is>
-      </c>
-      <c r="U97" s="5" t="inlineStr">
-        <is>
-          <t>Working simulation baseline; not final balance</t>
-        </is>
-      </c>
-      <c r="V97" s="5" t="inlineStr">
-        <is>
-          <t>Complete working profile</t>
-        </is>
-      </c>
-      <c r="W97" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="X97" s="5" t="inlineStr">
+      <c r="X97" s="6" t="inlineStr">
         <is>
           <t>Migrated from v0.8 baseline with v0.9 safety clarifications</t>
         </is>
@@ -63599,974 +63569,974 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
+          <t>AUG-WET-GROUND</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Wet Ground</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Terrain Effect</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Enemy Unit</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Water;  or Ground</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>Tiles affected by the supported Skill gain Wet for 1500 CT.</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>MP Cost ×1.15</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>As effect states</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>Once per supported resolution</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>At Skill commitment; remains through resolution</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>Original caster</t>
+        </is>
+      </c>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>As compatible Skill defines</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>Use normal terrain compatibility, ownership, duration, and element reactions.</t>
+        </is>
+      </c>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>Secondary effects do not inherit/retrigger this Augment.</t>
+        </is>
+      </c>
+      <c r="S98" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T98" s="6" t="inlineStr">
+        <is>
+          <t>Acquisition scarcity only; exact band pending</t>
+        </is>
+      </c>
+      <c r="U98" s="6" t="inlineStr">
+        <is>
+          <t>Working simulation baseline; not final balance</t>
+        </is>
+      </c>
+      <c r="V98" s="6" t="inlineStr">
+        <is>
+          <t>Complete working profile</t>
+        </is>
+      </c>
+      <c r="W98" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="X98" s="6" t="inlineStr">
+        <is>
+          <t>Migrated from v0.8 baseline with v0.9 safety clarifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
           <t>AUG-DELAY-STRIKE</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Delay Strike</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Timing</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>After dealing HP damage, increase target's CT for next turn by 20%.</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr">
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J98" s="6" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>MP Cost ×1.35</t>
         </is>
       </c>
-      <c r="K98" s="6" t="inlineStr">
+      <c r="K99" s="5" t="inlineStr">
         <is>
           <t>After successful HP damage</t>
         </is>
       </c>
-      <c r="L98" s="6" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M98" s="6" t="inlineStr">
+      <c r="M99" s="5" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N98" s="6" t="inlineStr">
+      <c r="N99" s="5" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O98" s="6" t="inlineStr">
+      <c r="O99" s="5" t="inlineStr">
         <is>
           <t>As compatible Skill defines</t>
         </is>
       </c>
-      <c r="P98" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q98" s="6" t="inlineStr">
+      <c r="P99" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q99" s="5" t="inlineStr">
         <is>
           <t>CT increase cannot exceed 2× target's base CT.</t>
         </is>
       </c>
-      <c r="R98" s="6" t="inlineStr">
+      <c r="R99" s="5" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S98" s="6" t="inlineStr">
+      <c r="S99" s="5" t="inlineStr">
         <is>
           <t>Max 1 CT delay per target per round from this Augment.</t>
         </is>
       </c>
-      <c r="T98" s="6" t="inlineStr">
+      <c r="T99" s="5" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U98" s="6" t="inlineStr">
+      <c r="U99" s="5" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V98" s="6" t="inlineStr">
+      <c r="V99" s="5" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W98" s="6" t="inlineStr">
+      <c r="W99" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X98" s="6" t="inlineStr">
+      <c r="X99" s="5" t="inlineStr">
         <is>
           <t>Turn denial. Delays enemy's next turn. Hard-capped to prevent perma-lock (max 1 per target per round).</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>AUG-INTERRUPT</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Interrupt</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Timing</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>Target must be channeling a skill</t>
         </is>
       </c>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>If target is currently channeling, the supported Skill cancels the channel. Channeled skill is wasted (costs still paid by target).</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J99" s="6" t="inlineStr">
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>MP Cost ×1.40</t>
         </is>
       </c>
-      <c r="K99" s="6" t="inlineStr">
+      <c r="K100" s="5" t="inlineStr">
         <is>
           <t>At damage resolution; channel check at resolution</t>
         </is>
       </c>
-      <c r="L99" s="6" t="inlineStr">
+      <c r="L100" s="5" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr">
+      <c r="M100" s="5" t="inlineStr">
         <is>
           <t>Condition evaluated at resolution</t>
         </is>
       </c>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="N100" s="5" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O99" s="6" t="inlineStr">
+      <c r="O100" s="5" t="inlineStr">
         <is>
           <t>As compatible Skill defines</t>
         </is>
       </c>
-      <c r="P99" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q99" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R99" s="6" t="inlineStr">
+      <c r="P100" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q100" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R100" s="5" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S99" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T99" s="6" t="inlineStr">
+      <c r="S100" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T100" s="5" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U99" s="6" t="inlineStr">
+      <c r="U100" s="5" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V99" s="6" t="inlineStr">
+      <c r="V100" s="5" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W99" s="6" t="inlineStr">
+      <c r="W100" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X99" s="6" t="inlineStr">
+      <c r="X100" s="5" t="inlineStr">
         <is>
           <t>Anti-channel utility. Punishes long-cast enemies. Conditional — does nothing if target isn't channeling. High MP cost reflects powerful disruption.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>AUG-MOMENTUM</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Timing</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>If the supported Skill defeats an enemy, caster's CT for next turn is reduced by 30%.</t>
         </is>
       </c>
-      <c r="I100" s="6" t="inlineStr">
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J100" s="6" t="inlineStr">
+      <c r="J101" s="5" t="inlineStr">
         <is>
           <t>MP Cost ×1.25</t>
         </is>
       </c>
-      <c r="K100" s="6" t="inlineStr">
+      <c r="K101" s="5" t="inlineStr">
         <is>
           <t>On qualifying direct KO</t>
         </is>
       </c>
-      <c r="L100" s="6" t="inlineStr">
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>Once per Skill execution</t>
         </is>
       </c>
-      <c r="M100" s="6" t="inlineStr">
+      <c r="M101" s="5" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N100" s="6" t="inlineStr">
+      <c r="N101" s="5" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O100" s="6" t="inlineStr">
+      <c r="O101" s="5" t="inlineStr">
         <is>
           <t>Primary Skill damage only</t>
         </is>
       </c>
-      <c r="P100" s="6" t="inlineStr">
+      <c r="P101" s="5" t="inlineStr">
         <is>
           <t>Primary Skill damage directly causes enemy KO</t>
         </is>
       </c>
-      <c r="Q100" s="6" t="inlineStr">
+      <c r="Q101" s="5" t="inlineStr">
         <is>
           <t>CT reduction cannot bring next turn below minimum CT threshold.</t>
         </is>
       </c>
-      <c r="R100" s="6" t="inlineStr">
+      <c r="R101" s="5" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S100" s="6" t="inlineStr">
+      <c r="S101" s="5" t="inlineStr">
         <is>
           <t>Max 1 trigger per unit turn.</t>
         </is>
       </c>
-      <c r="T100" s="6" t="inlineStr">
+      <c r="T101" s="5" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U100" s="6" t="inlineStr">
+      <c r="U101" s="5" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V100" s="6" t="inlineStr">
+      <c r="V101" s="5" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W100" s="6" t="inlineStr">
+      <c r="W101" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X100" s="6" t="inlineStr">
+      <c r="X101" s="5" t="inlineStr">
         <is>
           <t>Kill-conditional acceleration. Stronger than Quicken Self but requires a kill. Snowball potential — balanced by conditional nature.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>AUG-PRIORITY-SURGE</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>Priority Surge</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>Timing</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>Caster must be acting on first turn of a round (highest CT priority)</t>
         </is>
       </c>
-      <c r="H101" s="6" t="inlineStr">
+      <c r="H102" s="5" t="inlineStr">
         <is>
           <t>If caster acts first in the round, supported Skill gains +15% final damage.</t>
         </is>
       </c>
-      <c r="I101" s="6" t="inlineStr">
+      <c r="I102" s="5" t="inlineStr">
         <is>
           <t>Slot only</t>
         </is>
       </c>
-      <c r="J101" s="6" t="inlineStr">
+      <c r="J102" s="5" t="inlineStr">
         <is>
           <t>None — slot opportunity cost</t>
         </is>
       </c>
-      <c r="K101" s="6" t="inlineStr">
+      <c r="K102" s="5" t="inlineStr">
         <is>
           <t>At damage resolution; condition checked at commitment</t>
         </is>
       </c>
-      <c r="L101" s="6" t="inlineStr">
+      <c r="L102" s="5" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr">
+      <c r="M102" s="5" t="inlineStr">
         <is>
           <t>Condition evaluated at commitment</t>
         </is>
       </c>
-      <c r="N101" s="6" t="inlineStr">
+      <c r="N102" s="5" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O101" s="6" t="inlineStr">
+      <c r="O102" s="5" t="inlineStr">
         <is>
           <t>As compatible Skill defines</t>
         </is>
       </c>
-      <c r="P101" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q101" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R101" s="6" t="inlineStr">
+      <c r="P102" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q102" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R102" s="5" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S101" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T101" s="6" t="inlineStr">
+      <c r="S102" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T102" s="5" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U101" s="6" t="inlineStr">
+      <c r="U102" s="5" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V101" s="6" t="inlineStr">
+      <c r="V102" s="5" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W101" s="6" t="inlineStr">
+      <c r="W102" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X101" s="6" t="inlineStr">
+      <c r="X102" s="5" t="inlineStr">
         <is>
           <t>Rewards speed-built units. Conditional Amplifier crossover — filed under Timing because the condition is turn-order dependent.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>AUG-QUICKEN-SELF</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>Quicken Self</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>Timing</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Direct Damage</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>Enemy Unit</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>After the supported Skill resolves, reduce caster's CT (charge time) for next turn by 15%.</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
+      <c r="I103" s="5" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="J102" s="6" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>MP Cost ×1.30</t>
         </is>
       </c>
-      <c r="K102" s="6" t="inlineStr">
+      <c r="K103" s="5" t="inlineStr">
         <is>
           <t>After Skill resolution completes</t>
         </is>
       </c>
-      <c r="L102" s="6" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>Once per supported resolution</t>
         </is>
       </c>
-      <c r="M102" s="6" t="inlineStr">
+      <c r="M103" s="5" t="inlineStr">
         <is>
           <t>At Skill commitment; remains through resolution</t>
         </is>
       </c>
-      <c r="N102" s="6" t="inlineStr">
+      <c r="N103" s="5" t="inlineStr">
         <is>
           <t>Original caster</t>
         </is>
       </c>
-      <c r="O102" s="6" t="inlineStr">
+      <c r="O103" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P102" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q102" s="6" t="inlineStr">
+      <c r="P103" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q103" s="5" t="inlineStr">
         <is>
           <t>CT reduction cannot bring next turn below minimum CT threshold.</t>
         </is>
       </c>
-      <c r="R102" s="6" t="inlineStr">
+      <c r="R103" s="5" t="inlineStr">
         <is>
           <t>Secondary effects do not inherit/retrigger this Augment.</t>
         </is>
       </c>
-      <c r="S102" s="6" t="inlineStr">
+      <c r="S103" s="5" t="inlineStr">
         <is>
           <t>Max 1 CT reduction per unit turn from this Augment.</t>
         </is>
       </c>
-      <c r="T102" s="6" t="inlineStr">
+      <c r="T103" s="5" t="inlineStr">
         <is>
           <t>Acquisition scarcity only; exact band pending</t>
         </is>
       </c>
-      <c r="U102" s="6" t="inlineStr">
+      <c r="U103" s="5" t="inlineStr">
         <is>
           <t>Working simulation baseline; not final balance</t>
         </is>
       </c>
-      <c r="V102" s="6" t="inlineStr">
+      <c r="V103" s="5" t="inlineStr">
         <is>
           <t>Complete working profile</t>
         </is>
       </c>
-      <c r="W102" s="6" t="inlineStr">
+      <c r="W103" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X102" s="6" t="inlineStr">
+      <c r="X103" s="5" t="inlineStr">
         <is>
           <t>Self-acceleration. Act sooner next round by paying more MP now. Tempo augment for units that want frequent turns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>AUG-SLUGGISH-BLOW</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>Sluggish Blow</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>Direct Damage</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>Enemy Unit</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>After dealing HP damage, apply Slow status to target for 1 turn.</t>
-        </is>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="J103" s="6" t="inlineStr">
-        <is>
-          <t>MP Cost ×1.25</t>
-        </is>
-      </c>
-      <c r="K103" s="6" t="inlineStr">
-        <is>
-          <t>After successful HP damage</t>
-        </is>
-      </c>
-      <c r="L103" s="6" t="inlineStr">
-        <is>
-          <t>Once per supported resolution</t>
-        </is>
-      </c>
-      <c r="M103" s="6" t="inlineStr">
-        <is>
-          <t>At Skill commitment; remains through resolution</t>
-        </is>
-      </c>
-      <c r="N103" s="6" t="inlineStr">
-        <is>
-          <t>Original caster</t>
-        </is>
-      </c>
-      <c r="O103" s="6" t="inlineStr">
-        <is>
-          <t>As compatible Skill defines</t>
-        </is>
-      </c>
-      <c r="P103" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q103" s="6" t="inlineStr">
-        <is>
-          <t>Cannot support a Skill that already applies Slow.</t>
-        </is>
-      </c>
-      <c r="R103" s="6" t="inlineStr">
-        <is>
-          <t>Secondary effects do not inherit/retrigger this Augment.</t>
-        </is>
-      </c>
-      <c r="S103" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T103" s="6" t="inlineStr">
-        <is>
-          <t>Acquisition scarcity only; exact band pending</t>
-        </is>
-      </c>
-      <c r="U103" s="6" t="inlineStr">
-        <is>
-          <t>Working simulation baseline; not final balance</t>
-        </is>
-      </c>
-      <c r="V103" s="6" t="inlineStr">
-        <is>
-          <t>Complete working profile</t>
-        </is>
-      </c>
-      <c r="W103" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="X103" s="6" t="inlineStr">
-        <is>
-          <t>Status Delivery crossover filed under Timing. Applies Slow which directly affects turn order. Distinct from Delay Strike (CT push) — this uses the Slow status system.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
+          <t>AUG-SLUGGISH-BLOW</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Sluggish Blow</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Direct Damage</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Enemy Unit</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>After dealing HP damage, apply Slow status to target for 1 turn.</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>MP Cost ×1.25</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>After successful HP damage</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>Once per supported resolution</t>
+        </is>
+      </c>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
+          <t>At Skill commitment; remains through resolution</t>
+        </is>
+      </c>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>Original caster</t>
+        </is>
+      </c>
+      <c r="O104" s="5" t="inlineStr">
+        <is>
+          <t>As compatible Skill defines</t>
+        </is>
+      </c>
+      <c r="P104" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q104" s="5" t="inlineStr">
+        <is>
+          <t>Cannot support a Skill that already applies Slow.</t>
+        </is>
+      </c>
+      <c r="R104" s="5" t="inlineStr">
+        <is>
+          <t>Secondary effects do not inherit/retrigger this Augment.</t>
+        </is>
+      </c>
+      <c r="S104" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T104" s="5" t="inlineStr">
+        <is>
+          <t>Acquisition scarcity only; exact band pending</t>
+        </is>
+      </c>
+      <c r="U104" s="5" t="inlineStr">
+        <is>
+          <t>Working simulation baseline; not final balance</t>
+        </is>
+      </c>
+      <c r="V104" s="5" t="inlineStr">
+        <is>
+          <t>Complete working profile</t>
+        </is>
+      </c>
+      <c r="W104" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="X104" s="5" t="inlineStr">
+        <is>
+          <t>Status Delivery crossover filed under Timing. Applies Slow which directly affects turn order. Distinct from Delay Strike (CT push) — this uses the Slow status system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
           <t>AUG-EROSION</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Erosion</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>Elevation Mutation</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>Ground</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
         <is>
           <t>Elevation safety rules unresolved</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="H105" s="6" t="inlineStr">
         <is>
           <t>Not active</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R104" s="5" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R105" s="6" t="inlineStr">
         <is>
           <t>Not active; cannot recurse</t>
         </is>
       </c>
-      <c r="S104" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T104" s="5" t="inlineStr">
+      <c r="S105" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T105" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="U104" s="5" t="inlineStr">
+      <c r="U105" s="6" t="inlineStr">
         <is>
           <t>Parked</t>
         </is>
       </c>
-      <c r="V104" s="5" t="inlineStr">
+      <c r="V105" s="6" t="inlineStr">
         <is>
           <t>Parked intentionally</t>
         </is>
       </c>
-      <c r="W104" s="5" t="inlineStr">
+      <c r="W105" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X104" s="5" t="inlineStr">
-        <is>
-          <t>Bounds, occupied tiles, objectives, connectivity, objects, boundaries, and AI pathing remain parked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>AUG-RAISE-EARTH</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>Raise Earth</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>Elevation Mutation</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>Ground</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>Elevation safety rules unresolved</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>Not active</t>
-        </is>
-      </c>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R105" s="5" t="inlineStr">
-        <is>
-          <t>Not active; cannot recurse</t>
-        </is>
-      </c>
-      <c r="S105" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T105" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="U105" s="5" t="inlineStr">
-        <is>
-          <t>Parked</t>
-        </is>
-      </c>
-      <c r="V105" s="5" t="inlineStr">
-        <is>
-          <t>Parked intentionally</t>
-        </is>
-      </c>
-      <c r="W105" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="X105" s="5" t="inlineStr">
+      <c r="X105" s="6" t="inlineStr">
         <is>
           <t>Bounds, occupied tiles, objectives, connectivity, objects, boundaries, and AI pathing remain parked.</t>
         </is>
@@ -64575,859 +64545,981 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
+          <t>AUG-RAISE-EARTH</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Raise Earth</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Elevation Mutation</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>Elevation safety rules unresolved</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>Not active</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R106" s="6" t="inlineStr">
+        <is>
+          <t>Not active; cannot recurse</t>
+        </is>
+      </c>
+      <c r="S106" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T106" s="6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="U106" s="6" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="V106" s="6" t="inlineStr">
+        <is>
+          <t>Parked intentionally</t>
+        </is>
+      </c>
+      <c r="W106" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="X106" s="6" t="inlineStr">
+        <is>
+          <t>Bounds, occupied tiles, objectives, connectivity, objects, boundaries, and AI pathing remain parked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
           <t>REJ-DELAYED-REPETITION</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>Delayed Repetition</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>Requires excessive exceptions or creates farming/ownership risk</t>
         </is>
       </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>Rejected / superseded</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R106" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
         <is>
           <t>Cannot activate</t>
         </is>
       </c>
-      <c r="S106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T106" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U106" s="6" t="inlineStr">
+      <c r="S107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T107" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U107" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="V106" s="6" t="inlineStr">
+      <c r="V107" s="5" t="inlineStr">
         <is>
           <t>Complete rejection record</t>
         </is>
       </c>
-      <c r="W106" s="6" t="inlineStr">
+      <c r="W107" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X106" s="6" t="inlineStr">
+      <c r="X107" s="5" t="inlineStr">
         <is>
           <t>Design a new Skill instead if the concept remains desirable.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>REJ-FLEXIBLE-SELECTION</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>Flexible Selection</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>Requires excessive exceptions or creates farming/ownership risk</t>
         </is>
       </c>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>Rejected / superseded</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R107" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R108" s="5" t="inlineStr">
         <is>
           <t>Cannot activate</t>
         </is>
       </c>
-      <c r="S107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T107" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U107" s="6" t="inlineStr">
+      <c r="S108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T108" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U108" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="V107" s="6" t="inlineStr">
+      <c r="V108" s="5" t="inlineStr">
         <is>
           <t>Complete rejection record</t>
         </is>
       </c>
-      <c r="W107" s="6" t="inlineStr">
+      <c r="W108" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X107" s="6" t="inlineStr">
+      <c r="X108" s="5" t="inlineStr">
         <is>
           <t>Design a new Skill instead if the concept remains desirable.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>REJ-FORTUNE-STRIKE</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>Fortune Strike</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>Requires excessive exceptions or creates farming/ownership risk</t>
         </is>
       </c>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>Rejected / superseded</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R108" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R109" s="5" t="inlineStr">
         <is>
           <t>Cannot activate</t>
         </is>
       </c>
-      <c r="S108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T108" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U108" s="6" t="inlineStr">
+      <c r="S109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T109" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U109" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="V108" s="6" t="inlineStr">
+      <c r="V109" s="5" t="inlineStr">
         <is>
           <t>Complete rejection record</t>
         </is>
       </c>
-      <c r="W108" s="6" t="inlineStr">
+      <c r="W109" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X108" s="6" t="inlineStr">
+      <c r="X109" s="5" t="inlineStr">
         <is>
           <t>Design a new Skill instead if the concept remains desirable.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>REJ-GENERAL-TARGET-BASIS-REPLACEMENT</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>General Target-Basis Replacement</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
         <is>
           <t>Requires excessive exceptions or creates farming/ownership risk</t>
         </is>
       </c>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="H110" s="5" t="inlineStr">
         <is>
           <t>Rejected / superseded</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R109" s="6" t="inlineStr">
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R110" s="5" t="inlineStr">
         <is>
           <t>Cannot activate</t>
         </is>
       </c>
-      <c r="S109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T109" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U109" s="6" t="inlineStr">
+      <c r="S110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T110" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U110" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="V109" s="6" t="inlineStr">
+      <c r="V110" s="5" t="inlineStr">
         <is>
           <t>Complete rejection record</t>
         </is>
       </c>
-      <c r="W109" s="6" t="inlineStr">
+      <c r="W110" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X109" s="6" t="inlineStr">
+      <c r="X110" s="5" t="inlineStr">
         <is>
           <t>Design a new Skill instead if the concept remains desirable.</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>REJ-GOLD-ON-HIT</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>Gold on Hit</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>Requires excessive exceptions or creates farming/ownership risk</t>
         </is>
       </c>
-      <c r="H110" s="6" t="inlineStr">
+      <c r="H111" s="5" t="inlineStr">
         <is>
           <t>Rejected / superseded</t>
         </is>
       </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R110" s="6" t="inlineStr">
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R111" s="5" t="inlineStr">
         <is>
           <t>Cannot activate</t>
         </is>
       </c>
-      <c r="S110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T110" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U110" s="6" t="inlineStr">
+      <c r="S111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T111" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U111" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="V110" s="6" t="inlineStr">
+      <c r="V111" s="5" t="inlineStr">
         <is>
           <t>Complete rejection record</t>
         </is>
       </c>
-      <c r="W110" s="6" t="inlineStr">
+      <c r="W111" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X110" s="6" t="inlineStr">
+      <c r="X111" s="5" t="inlineStr">
         <is>
           <t>Design a new Skill instead if the concept remains desirable.</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>REJ-GROUNDED-CASTING</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>Grounded Casting</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>Requires excessive exceptions or creates farming/ownership risk</t>
         </is>
       </c>
-      <c r="H111" s="6" t="inlineStr">
+      <c r="H112" s="5" t="inlineStr">
         <is>
           <t>Rejected / superseded</t>
         </is>
       </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R111" s="6" t="inlineStr">
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R112" s="5" t="inlineStr">
         <is>
           <t>Cannot activate</t>
         </is>
       </c>
-      <c r="S111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T111" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U111" s="6" t="inlineStr">
+      <c r="S112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T112" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U112" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="V111" s="6" t="inlineStr">
+      <c r="V112" s="5" t="inlineStr">
         <is>
           <t>Complete rejection record</t>
         </is>
       </c>
-      <c r="W111" s="6" t="inlineStr">
+      <c r="W112" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X111" s="6" t="inlineStr">
+      <c r="X112" s="5" t="inlineStr">
         <is>
           <t>Design a new Skill instead if the concept remains desirable.</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>REJ-PURSUING-EFFECT</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>Pursuing Effect</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>Requires excessive exceptions or creates farming/ownership risk</t>
         </is>
       </c>
-      <c r="H112" s="6" t="inlineStr">
+      <c r="H113" s="5" t="inlineStr">
         <is>
           <t>Rejected / superseded</t>
         </is>
       </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R112" s="6" t="inlineStr">
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R113" s="5" t="inlineStr">
         <is>
           <t>Cannot activate</t>
         </is>
       </c>
-      <c r="S112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T112" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U112" s="6" t="inlineStr">
+      <c r="S113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T113" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U113" s="5" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="V112" s="6" t="inlineStr">
+      <c r="V113" s="5" t="inlineStr">
         <is>
           <t>Complete rejection record</t>
         </is>
       </c>
-      <c r="W112" s="6" t="inlineStr">
+      <c r="W113" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X112" s="6" t="inlineStr">
+      <c r="X113" s="5" t="inlineStr">
         <is>
           <t>Design a new Skill instead if the concept remains desirable.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X112"/>
+  <autoFilter ref="A1:X113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -35,6 +35,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16 Terrain Effects" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17 Objects Encounters" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18 Open Decisions" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Persistent HP MP" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Project Identity'!$A$1:$D$79</definedName>
@@ -36522,6 +36523,693 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PERSISTENT HP/MP AND RECOVERY RULES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Post-battle recovery, KO handling, MP regen, base behavior, deployment, and Max HP/MP change rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: CTRBLXAI.db persistent_hp_mp_rules (25 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Persistent Resources</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Battle Start</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Battle Start HP = Persistent Current HP. Battle Start MP = Persistent Current MP. Starting a battle does not refill either resource.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Persistent Resources</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New Unit Init</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Newly created or recruited units initialize at full HP and full MP once. Not a recurring battle-start rule.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Post-Battle Recovery</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Recovery Formula</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>After every qualifying completed battle, each surviving owned unit recovers: HP Recovery = ceil(Max HP × 0.35), MP Recovery = ceil(Max MP × 0.35). Current = min(Max, Current + Recovery).</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>35% is working value; verify through expedition testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Post-Battle Recovery</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Deployed and Benched</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Recovery applies to ALL surviving owned units whether deployed or benched. A unit at 0% would reach full after ~3 qualifying battles.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Post-Battle Recovery</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Qualifying Battle</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Recovery triggers only when encounter completes legitimate victory requirements and runs normal completion processing. Abandoned, cancelled, failed-to-init, dev-test, or zero-completion do not grant recovery.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Post-Battle Recovery</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Victory met → finish current action + triggered resolutions → persist final HP/MP/Item charges → apply post-battle recovery → end battle.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Post-Battle Recovery</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No Free Phase</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Once victory requirements satisfied, battle ends after active resolution chain. Players cannot continue casting, using Items, regenerating, or repositioning. Use recovery Skills BEFORE the finishing action.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KO Rules</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KO Penalty</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KO units receive NO post-battle HP or MP recovery. Remain KO until roster returns to base.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KO Rules</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Base Clears KO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Returning to base clears KO first during base processing. Unit receives Current HP = 1. Current MP unchanged (stays at whatever it was at KO). Returning to base does NOT otherwise restore HP or MP.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Locked. 1 HP is intentionally harsh — unit needs recovery battles or healing Items before being combat-ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KO Rules</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Design Intent</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KO is materially worse than surviving at low HP without requiring permanent injury or death.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Natural MP Regen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MP Regen = 2 + floor(INT / 40) MP per 1000 CT. Base 2 ensures all units regenerate naturally. Every 40 INT adds +1. No cap. Accumulator += CT Passed × MP Regen / 1000. When Accumulator ≥ 1: restore floor(Accumulator) MP, retain fraction.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Coefficient 6 is working value; test against Skill MP costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Natural MP Regen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Visible Derived Stat. Linear formula: base 2 + floor(INT/40). Based on elapsed CT (not ready turns) so fast units do not regenerate more. No cap. Intentionally provides baseline recovery to all units while rewarding INT investment at clear breakpoints.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Natural MP Regen</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Reference Table</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>INT 0=2, INT 40=3, INT 80=4, INT 120=5, INT 160=6, INT 200=7, INT 240=8, INT 300=9 MP per 1000 CT.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Natural MP Regen</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Only progresses while battle CT is advancing. Does not progress while paused, disconnected, loading, or waiting in decision menu where CT is stopped.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Recovery Stalling</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No cap on natural MP regen, no reward for fast victories, no penalty for long battles. Deliberate stalling is allowed — elapsed time, AP, RT, MP costs, and Item charges are accepted opportunity costs.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Recovery Stalling</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Instant or zero-time resource-positive loops remain invalid. A repeatable effect must not restore more MP than it spends without elapsed CT, a finite charge, a sacrifice, or another real resource.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Base Rules</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Items at Base</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Items cannot be used at base. Returning to base replenishes all charged Item uses. Because Items cannot be activated at base, charge replenishment cannot convert into unlimited HP/MP recovery.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Base Rules</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Base Does Not Heal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Returning to base does NOT restore HP or MP. Only clears KO and replenishes Item charges.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Max Resource Changes</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Max Increases</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>If Maximum increases: Current Resource += New Maximum − Old Maximum. Preserves amount missing.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Max Resource Changes</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Max Decreases</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>If Maximum decreases: Current Resource = min(Current Resource, New Maximum). Clamps without conversion.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Passive Interactions</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Arcane Flow</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Remains explicit ready-turn MP recovery passive (not CT-based). Does not become part of MP Regen stat. Value may need retest after persistent MP implemented.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Passive Interactions</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Intentionally both hard control AND expedition recovery tool. Sleeping units recover HP/MP per Sleep rule. Allowing enemy to stay asleep also lets enemy recover — tactical risk.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Passive Interactions</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quiver Quick Draw</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Retains 10% Max MP activation payment as working value. Persistent MP makes this more consequential. Adjust only after playtesting.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deployment UI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Resource Readiness</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Deployment interface must expose: Current HP/Max HP, Current MP/Max MP, Item charges, KO status. Warn when team has low HP, low MP, depleted Items, or KO members. Warning informs but does not block deployment.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Starter Support</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Starting Items</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Starting units receive existing Small Healing Potions and Ether Cell. No tutorial-only consumable. Early tutorial should demonstrate Item use + base charge replenishment.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -36,6 +36,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17 Objects Encounters" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18 Open Decisions" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Persistent HP MP" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 Item Affix Names" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Project Identity'!$A$1:$D$79</definedName>
@@ -38861,6 +38862,3198 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E165"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ITEM AFFIX NAME CATALOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Prefix/suffix names for procedurally generated equipment. Highest BP bonus = prefix, second-highest = suffix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: CTRBLXAI.db item_affix_names (153 entries)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Source Family</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Affix Name</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AGI Bonus</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Nimble</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AGI Bonus</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AGI Bonus</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Flickering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AGI Bonus</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tempest</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AGI Bonus</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Phantom</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AGI Bonus</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Windborn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Collision Damage</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ramming</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Collision Damage</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Crushing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Collision Damage</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Shattering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Collision Damage</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Obliterating</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Collision Resistance</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Braced</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Collision Resistance</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Anchored</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Collision Resistance</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Immovable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Collision Resistance</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Unshakable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DEX Bonus</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DEX Bonus</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Deft</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DEX Bonus</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Masterwork</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DEX Bonus</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Razortuned</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DEX Bonus</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Flawless</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DEX Bonus</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sovereign</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Debuff Resistance</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cleansing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Debuff Resistance</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Purifying</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Debuff Resistance</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sanctified</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Debuff Resistance</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Incorruptible</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Equipment Defense</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plated</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Equipment Defense</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Reinforced</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Equipment Defense</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bastion</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Equipment Defense</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Impervious</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Equipment Defense</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Adamantine</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Evasiveness</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Elusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Evasiveness</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ghostly</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Evasiveness</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Shadowdancer's</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Evasiveness</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Untouchable</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fall Damage Decrease</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cushioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fall Damage Decrease</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Catfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fall Damage Decrease</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Featherfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fall Damage Decrease</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Cloudwalker's</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fall Resistance</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fall Resistance</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Steadfast</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Fall Resistance</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Rootbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Fall Resistance</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Earthlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Prosperous</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Gilded</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fateweaver's</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Miraculous</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Vital</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Enduring</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Lifebound</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Undying</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Immortal</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Healing Output</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mending</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Healing Output</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Restorative</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Healing Output</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lifegiver's</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Healing Output</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Asclepian</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>INT Bonus</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Keen</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>INT Bonus</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Arcane</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>INT Bonus</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Brilliant</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>INT Bonus</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sagefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>INT Bonus</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Transcendent</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>INT Bonus</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Omniscient</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Item Direct Damage</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Volatile</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Item Direct Damage</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Explosive</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Item Direct Damage</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Cataclysmic</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Item Direct Damage</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ruinous</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LUK Bonus</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lucky</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LUK Bonus</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Fortunate</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LUK Bonus</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Fateblessed</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LUK Bonus</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Starborn</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LUK Bonus</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LUK Bonus</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Destined</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Channeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Resonant</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Spellwoven</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Manaforged</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Infinite</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Marksman's</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Deadeye</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Unerring</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RT Delay Resistance</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Resolute</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RT Delay Resistance</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Ironwilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RT Delay Resistance</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Unfaltering</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RT Delay Resistance</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Indomitable</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>STR Bonus</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sturdy</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>STR Bonus</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mighty</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>STR Bonus</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Herculean</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>STR Bonus</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Titanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>STR Bonus</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>5</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Colossal</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>STR Bonus</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>6</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Godslayer's</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Skill Potency</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Empowered</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Skill Potency</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Overcharged</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Skill Potency</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Cataclyst's</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Skill Potency</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Worldbreaker's</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VIT Bonus</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Hardy</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>VIT Bonus</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Stalwart</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VIT Bonus</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Ironhide</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VIT Bonus</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Unyielding</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>VIT Bonus</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Mountainborn</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>VIT Bonus</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>6</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Eternal</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Weapon Attack</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Honed</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Weapon Attack</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Brutal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Weapon Attack</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Vicious</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Weapon Attack</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Devastating</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Weapon Attack</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>5</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Annihilating</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Weapon Defense</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Warding</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Weapon Defense</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Deflecting</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Weapon Defense</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Bulwark</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Weapon Defense</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Weapon RT Delay</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Staggering</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Weapon RT Delay</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Jarring</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Weapon RT Delay</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Concussive</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Weapon RT Delay</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Crippling</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Weight Reduction</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Weight Reduction</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Featherweight</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Weight Reduction</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Weightless</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Weight Reduction</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>4</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Ethereal</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>numerical</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Weight Reduction</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Void-Touched</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PAS-001</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Brutality</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PAS-002</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Swiftness</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PAS-003</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PAS-004</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sundering</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PAS-005</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Vampirism</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PAS-006</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Vengeance</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PAS-007</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>the Tempest</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PAS-008</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PAS-009</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Cleaving</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PAS-010</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Dominion</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PAS-011</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Affliction</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PAS-012</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Searing</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PAS-013</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Frost</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PAS-014</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Thunder</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PAS-015</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Silence</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PAS-016</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Binding</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PAS-017</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>the Bulwark</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PAS-018</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>the Fortress</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PAS-019</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Retribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PAS-020</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Endurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PAS-021</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>the Phoenix</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PAS-022</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PAS-023</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Ambush</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PAS-024</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>the Hawk</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PAS-025</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Siphoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PAS-026</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Channeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PAS-027</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Overflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PAS-028</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Displacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PAS-029</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>the Colossus</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PAS-030</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Piercing</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PAS-031</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>the Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PAS-032</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>the Sentinel</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PAS-033</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Shattering</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PAS-034</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>the Mystic</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PAS-035</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Harvesting</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PAS-036</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>the Warden</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>═══ COMPOSITION RULES ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>0 bonuses (Broken/Common)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>BaseName</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Flameberge</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1 bonus</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>[Prefix] BaseName</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Mighty Flameberge</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2+ bonuses</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>[Prefix] BaseName of [Suffix]</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Mighty Flameberge of Searing</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Tie-breaking</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Passive wins over numerical, then alphabetical family name</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -37,6 +37,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18 Open Decisions" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Persistent HP MP" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 Item Affix Names" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Unit Progression" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Project Identity'!$A$1:$D$79</definedName>
@@ -42054,6 +42055,664 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UNIT XP AND LEVELING SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Completion XP + procedural objective bonuses. Objectives generated from encounter content, not authored per encounter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XP Model</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Completion + Procedural Objective Bonus. Base XP per battle completion, bonus XP from procedurally generated objectives derived from encounter content.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XP Model</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fell Seal (objective bonuses) + Crawl Tactics (procedural encounters) hybrid. Objectives are NOT authored per encounter — they are generated from spawned content.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Award timing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>XP awarded after battle completion. All deployed units receive base XP. Benched units receive 50%.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Base formula</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Base XP = Encounter Base XP × Level Scaling Factor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Locked direction — exact values pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Level Scaling Factor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Diminishing returns when unit level exceeds encounter level. Bonus when underleveled. Exact formula pending.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Encounter Base XP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Authored per encounter type: normal, elite, boss, quest. Exact values pending.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anti-farming</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trivial content provides sharply reduced XP. Same direction as Guild XP anti-farming rule.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Human passive</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Human Adaptability: EXP gained +10%. Applied to total XP (base + bonuses).</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Locked — references races table</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Benched units</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Deployed units receive 100% XP. Benched owned units receive 50%. Prevents permanent roster gaps.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Base XP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KO units</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KO'd units still receive XP if battle is won. They participated.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Level Curve</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>XP to next level = floor(100 × Level^1.4). Exact exponent and base pending simulation.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Working baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Level Curve</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Reference values</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>L1→2: 100 XP. L10→11: ~2,512 XP. L50→51: ~36,840 XP. L99 cap.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Working baseline — pending simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Level Curve</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Level cap</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>99. No XP earned past cap.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Level Curve</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Stat gain on level-up</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Base stats recalculated from race growth rates: baseStat = startingStat + floor(growthRate × (level - 1)). Already implemented in RaceData.CalcBaseStats.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Locked — already functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Objectives are generated from encounter content at battle start, not authored per encounter. Each spawned feature may create an objective.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Objective sources</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Objectives derive from what the encounter generator placed: elite enemies, NPCs, map objects, terrain features, spawn timing, enemy composition.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bonus range</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Each objective grants 10-50% bonus XP on top of base. Multiple objectives may be active. All are optional.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Locked direction — exact values pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Player visibility</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Active objectives shown at battle start and during battle. Completion shown in real-time. Final summary at battle end.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No penalty</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Failing an objective grants zero bonus — never reduces base XP. Objectives are purely additive.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Elite enemy spawned</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Defeat the elite enemy within N turns. Bonus: 25-40%.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Example — values pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NPC spawned</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Protect the NPC — NPC survives the battle. Bonus: 20-30%.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Example — values pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Siege object spawned</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hit N enemies with the ballista/catapult. Bonus: 15-25%.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Example — values pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Speed objective</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Win within N turns. Turn count scales with encounter size. Bonus: 15-25%.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Example — always available</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Flawless objective</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>No unit KO'd. Bonus: 20-30%.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Example — always available</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All defeated</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Defeat all enemies (not just win condition). Bonus: 10-15%.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Example — always available</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Functional owner</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Slice 6 owns XP system design and implementation. Unit Level already exists as a field. RaceData.CalcBaseStats already recalculates stats from level.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Slice 5 (procedural maps) must exist before procedural objectives can detect spawned content. Base XP (completion only) can work without Slice 5.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Guild XP relationship</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unit XP and Guild XP are separate systems. Guild XP is account-wide progression. Unit XP is per-unit stat progression. Both award after battle completion.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -42061,7 +42061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42074,7 +42074,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Completion XP + procedural objective bonuses. Objectives generated from encounter content, not authored per encounter.</t>
+          <t>Kill-based XP + procedural objectives. Linear ramp: XP to level = 500 + (Level × 20). L99 cap at launch. Evolutions post-launch.</t>
         </is>
       </c>
     </row>
@@ -42113,12 +42113,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Completion + Procedural Objective Bonus. Base XP per battle completion, bonus XP from procedurally generated objectives derived from encounter content.</t>
+          <t>Completion + Procedural Objective Bonus. Base XP per enemy killed, scaling with enemy level. Bonus XP from procedurally generated objectives. Quest board shows biome, rewards, and XP range upfront. XP requirement grows with level — early levels fast, later levels slower.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Locked direction</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
@@ -42130,12 +42130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>XP per kill</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fell Seal (objective bonuses) + Crawl Tactics (procedural encounters) hybrid. Objectives are NOT authored per encounter — they are generated from spawned content.</t>
+          <t>Kill XP = Base Type XP × (1 + Enemy Level / 50). Higher level enemies give more XP.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -42147,281 +42147,281 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>XP Model</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Award timing</t>
+          <t>Quest display</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>XP awarded after battle completion. All deployed units receive base XP. Benched units receive 50%.</t>
+          <t>Quest board shows: biome, quest type, recommended level, enemy count range, reward drops, gold, and XP range (min-max based on enemies defeated).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Locked direction</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>Enemy Base XP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Base formula</t>
+          <t>Grunt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Base XP = Encounter Base XP × Level Scaling Factor</t>
+          <t>20 XP base. Standard filler enemy.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Locked direction — exact values pending</t>
+          <t>Working baseline</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>Enemy Base XP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Level Scaling Factor</t>
+          <t>Veteran</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Diminishing returns when unit level exceeds encounter level. Bonus when underleveled. Exact formula pending.</t>
+          <t>35 XP base. Tier 1+ standard, Tier 0 rare.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Working baseline</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>Enemy Base XP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Encounter Base XP</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Authored per encounter type: normal, elite, boss, quest. Exact values pending.</t>
+          <t>60 XP base. 1-2 per quest when present.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Working baseline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>Enemy Base XP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anti-farming</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trivial content provides sharply reduced XP. Same direction as Guild XP anti-farming rule.</t>
+          <t>120 XP base. Quest objective, usually 1.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Locked direction</t>
+          <t>Working baseline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>Kill XP Scaling</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Human passive</t>
+          <t>Grunt L1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Human Adaptability: EXP gained +10%. Applied to total XP (base + bonuses).</t>
+          <t>20 × (1 + 1/50) = 20 XP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Locked — references races table</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>Kill XP Scaling</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Benched units</t>
+          <t>Grunt L50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deployed units receive 100% XP. Benched owned units receive 50%. Prevents permanent roster gaps.</t>
+          <t>20 × (1 + 50/50) = 40 XP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Base XP</t>
+          <t>Kill XP Scaling</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KO units</t>
+          <t>Grunt L99</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KO'd units still receive XP if battle is won. They participated.</t>
+          <t>20 × (1 + 99/50) = 60 XP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Locked direction</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Level Curve</t>
+          <t>Kill XP Scaling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Grunt L150</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>XP to next level = floor(100 × Level^1.4). Exact exponent and base pending simulation.</t>
+          <t>20 × (1 + 150/50) = 80 XP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Working baseline</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Level Curve</t>
+          <t>Kill XP Scaling</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reference values</t>
+          <t>Grunt L250</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L1→2: 100 XP. L10→11: ~2,512 XP. L50→51: ~36,840 XP. L99 cap.</t>
+          <t>20 × (1 + 250/50) = 120 XP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Working baseline — pending simulation</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Level Curve</t>
+          <t>Kill XP Scaling</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Level cap</t>
+          <t>Elite L99</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>99. No XP earned past cap.</t>
+          <t>60 × (1 + 99/50) = 179 XP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Level Curve</t>
+          <t>Kill XP Scaling</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stat gain on level-up</t>
+          <t>Boss L200</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Base stats recalculated from race growth rates: baseStat = startingStat + floor(growthRate × (level - 1)). Already implemented in RaceData.CalcBaseStats.</t>
+          <t>120 × (1 + 200/50) = 600 XP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Locked — already functional</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>Evolution Tiers</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Future tiers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Objectives are generated from encounter content at battle start, not authored per encounter. Each spawned feature may create an objective.</t>
+          <t>Additional evolution tiers extend by adding one XP/level value. Clean extension.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -42433,83 +42433,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>Level Curve</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Objective sources</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Objectives derive from what the encounter generator placed: elite enemies, NPCs, map objects, terrain features, spawn timing, enemy composition.</t>
+          <t>Linear ramp: XP to next level = 500 + (Level × 20). Higher levels require more XP. This counteracts enemy-level kill scaling to produce natural pacing: early levels ~4 battles, late levels ~6-7 battles.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Locked direction</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>Level Curve</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bonus range</t>
+          <t>Level cap</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Each objective grants 10-50% bonus XP on top of base. Multiple objectives may be active. All are optional.</t>
+          <t>99 at launch. Racial evolutions (extending to 199, 299) are post-launch features. Tier 1 and Tier 2 XP formulas will be set when evolutions release, informed by live player data.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Locked direction — exact values pending</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>Level Curve</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Player visibility</t>
+          <t>Stat gain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Active objectives shown at battle start and during battle. Completion shown in real-time. Final summary at battle end.</t>
+          <t>Base stats recalculated from race growth rates: baseStat = startingStat + floor(growthRate × (level - 1)). Already implemented in RaceData.CalcBaseStats.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Locked direction</t>
+          <t>Locked — already functional</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>XP Distribution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>No penalty</t>
+          <t>Battle formula</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Failing an objective grants zero bonus — never reduces base XP. Objectives are purely additive.</t>
+          <t>Battle XP = sum of (Base Type XP × (1 + Enemy Level / 50)) for each enemy defeated. Plus objective bonuses.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -42521,190 +42521,850 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>XP Distribution</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Elite enemy spawned</t>
+          <t>Deployed units</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Defeat the elite enemy within N turns. Bonus: 25-40%.</t>
+          <t>100% of battle XP.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Example — values pending</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>XP Distribution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NPC spawned</t>
+          <t>Benched units</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Protect the NPC — NPC survives the battle. Bonus: 20-30%.</t>
+          <t>50% of battle XP. Prevents permanent roster gaps.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Example — values pending</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>XP Distribution</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Siege object spawned</t>
+          <t>KO'd units</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hit N enemies with the ballista/catapult. Bonus: 15-25%.</t>
+          <t>Receive full XP if battle is won. They participated.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Example — values pending</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>XP Distribution</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Speed objective</t>
+          <t>Human passive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Win within N turns. Turn count scales with encounter size. Bonus: 15-25%.</t>
+          <t>Adaptability: total XP (kills + objectives) × 1.10.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Example — always available</t>
+          <t>Locked — references races table</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>Level Scaling</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Flawless objective</t>
+          <t>On-level (gap ≤5)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No unit KO'd. Bonus: 20-30%.</t>
+          <t>×1.0 — no penalty.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Example — always available</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Procedural Objectives</t>
+          <t>Level Scaling</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>All defeated</t>
+          <t>Gap 6-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Defeat all enemies (not just win condition). Bonus: 10-15%.</t>
+          <t>×0.75</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Example — always available</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ownership</t>
+          <t>Level Scaling</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Functional owner</t>
+          <t>Gap 11-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slice 6 owns XP system design and implementation. Unit Level already exists as a field. RaceData.CalcBaseStats already recalculates stats from level.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>×0.50</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ownership</t>
+          <t>Level Scaling</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Gap 16-20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slice 5 (procedural maps) must exist before procedural objectives can detect spawned content. Base XP (completion only) can work without Slice 5.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>×0.25</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Level Scaling</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gap 21+</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>×0.10 — trivial content.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Level Scaling</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Underleveled ≤-5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>×1.25</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Level Scaling</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Underleveled ≤-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>×1.50 (cap)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Level Scaling</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Level Gap = Unit Level - Quest Recommended Level. Multiplier applied to all kill XP.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Generated from encounter content at battle start. Not authored per encounter. Each spawned feature may create an objective. All optional — failure never reduces base XP.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Elite spawned</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Defeat the elite within N turns. Bonus: 25-40% of base XP.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Working baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NPC spawned</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NPC survives the battle. Bonus: 20-30%.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Working baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Siege object</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Hit N enemies with ballista/catapult. Bonus: 15-25%.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Working baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Speed clear</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Win within N turns (scales with encounter size). Bonus: 15-25%. Always available.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Working baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Flawless</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>No unit KO'd. Bonus: 20-30%. Always available.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Working baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Procedural Objectives</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>All defeated</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Defeat all enemies (not just win condition). Bonus: 10-15%. Always available.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Working baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Quest Types</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Normal battle</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Standard combat encounter. XP from kills.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Quest Types</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Elite battle</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Contains elite enemies. Higher XP per kill.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Quest Types</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Boss battle</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Contains boss enemy. Highest per-kill XP.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Quest Types</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Slay X</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Defeat X specific enemies. Kill count determines XP.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Quest Types</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Survive</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Survive N turns. Minimum XP guaranteed on completion. Enemies defeated add additional XP.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Quest Types</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Protect NPC/object. Minimum XP guaranteed. Enemies defeated add additional XP.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Quest Types</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Series of battles. Each battle awards XP separately. Total = sum of individual battles.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dispatched units earn flat XP based on dispatch difficulty × duration. Unit unavailable for N battles.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>XP formula</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dispatch XP = Dispatch Difficulty XP × Duration Multiplier. Roughly equivalent to one battle's kills as tradeoff for no player control.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Locked direction — exact values pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Anti-Farming</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Trivial content provides sharply reduced XP via overleveled penalty. Same direction as Guild XP anti-farming.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>Ownership</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Functional owner</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Slice 6 owns XP system implementation. Base formula can work without Slice 5. Procedural objectives need Slice 5 map spawns.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Slice 5: procedural maps for objectives. Slice 8: quest board, dispatch, exploration. Daily/seasonal events: separate reward systems, may grant XP as part of reward.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Guild XP relationship</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Unit XP and Guild XP are separate systems. Guild XP is account-wide progression. Unit XP is per-unit stat progression. Both award after battle completion.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Unit XP and Guild XP are separate. Guild XP = account progression (merchants, facilities). Unit XP = per-unit stat progression. Both award after battle. Separate formulas.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Platform Features</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Seasonal events</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Top players can become random boss encounters. Limited-time Unique rarity items. Special event XP sources possible.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Locked direction — Roblox live-service features</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Platform Features</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Daily events</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Special resources (e.g., item level-up materials). May include XP bonuses.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Platform Features</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Progression breadth</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Leveling is one of many parallel systems: Guild Level, equipment rarity, loadout customization, quest variety, exploration, dispatch, seasonal events, daily events. Level cap is a long-term milestone, not the only goal.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Level Curve</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>XP to next level = 500 + (Level × 20). L1→2: 520 XP. L10→11: 700 XP. L25→26: 1,000 XP. L50→51: 1,500 XP. L75→76: 2,000 XP. L98→99: 2,460 XP.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Evolution Tiers</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Launch (Tier 0)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Level 1-99. XP to next level = 500 + (Level × 20). No evolutions at launch. Total XP L1→99: ~145,000 XP.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Evolution Tiers</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Post-launch evolutions</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1st Evolution (L100-199): unlocks Skill Slot 5, improved racial perk/drawback. 2nd Evolution (L200-299): unlocks 2nd Doctrine slot, further improved racials. XP formulas for Tier 1 and 2 set at release using live data.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Evolution Tiers</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Future tiers</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Additional evolution tiers extend level cap. Formula calibrated from live data at each release.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
         </is>
       </c>
     </row>
